--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/To_convert_GTG_ITEM_NAME_to_match_our_ITEM_NAME/OUTPUT_converted_GTG_foR_RAW_DB.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/To_convert_GTG_ITEM_NAME_to_match_our_ITEM_NAME/OUTPUT_converted_GTG_foR_RAW_DB.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,14 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>120</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>120/48</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120 CONTINOUS POLYESTER FILAMENT  5GPD </t>
+          <t xml:space="preserve">120/48 CONTINOUS POLYESTER FILAMENT  5GPD </t>
         </is>
       </c>
     </row>
@@ -508,12 +510,14 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>150</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>150/48</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>150 TEXTURISED POLYESTER</t>
+          <t>150/48 TEXTURISED POLYESTER</t>
         </is>
       </c>
     </row>
@@ -540,12 +544,14 @@
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>150</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>150/48</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>150 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>150/48 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1104,14 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>210</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>210/24</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>210 HI-TENACITY NYLON 6 YARN</t>
+          <t>210/24 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1138,14 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>210</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>210/24</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>210 HI-TENACITY NYLON 6 YARN</t>
+          <t>210/24 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1176,14 @@
           <t>BLACK DopeDyed</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>210</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>210/34</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">210 HI-TENACITY NYLON 6 YARN </t>
+          <t xml:space="preserve">210/34 HI-TENACITY NYLON 6 YARN </t>
         </is>
       </c>
     </row>
@@ -1198,12 +1210,14 @@
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="n">
-        <v>210</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>210/48</t>
+        </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>210 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/48 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1244,14 @@
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>210</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>210/48</t>
+        </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>210 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/48 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1278,14 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="n">
-        <v>210</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>210/48</t>
+        </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>210 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/48 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1312,14 @@
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="n">
-        <v>210</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>210/72</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>210 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/72 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1346,14 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="n">
-        <v>210</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>210/72</t>
+        </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>210 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>210/72 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1380,14 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="n">
-        <v>250</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>250/48</t>
+        </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>250 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>250/48 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1414,14 @@
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="n">
-        <v>250</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>250/72</t>
+        </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>250 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>250/72 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1592,12 +1618,14 @@
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="n">
-        <v>30</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>30/14</t>
+        </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>30 LMY NYLON</t>
+          <t>30/14 LMY NYLON</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1652,14 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="n">
-        <v>30</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>30/14</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>30 LMY POLYESTER</t>
+          <t>30/14 LMY POLYESTER</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1724,14 @@
           <t xml:space="preserve"> BLACK DopeDyed</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>420</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>420/144</t>
+        </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>420 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>420/144 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1758,14 @@
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="n">
-        <v>420</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>420/144</t>
+        </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>420 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>420/144 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1792,14 @@
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="n">
-        <v>420</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>420/48</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>420 HI-TENACITY NYLON 6 YARN</t>
+          <t>420/48 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1826,14 @@
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="n">
-        <v>420</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>420/48</t>
+        </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>420 HI-TENACITY NYLON 6 YARN</t>
+          <t>420/48 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1860,14 @@
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="n">
-        <v>420</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>420/72</t>
+        </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>420 HI-TENACITY NYLON 66 YARN</t>
+          <t>420/72 HI-TENACITY NYLON 66 YARN</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1894,14 @@
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="n">
-        <v>420</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>420/96</t>
+        </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>420 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>420/96 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1928,14 @@
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="n">
-        <v>50</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>50/36</t>
+        </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50 LMY NYLON</t>
+          <t>50/36 LMY NYLON</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1962,14 @@
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="n">
-        <v>50</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>50/36</t>
+        </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50 LMY POLYESTER</t>
+          <t>50/36 LMY POLYESTER</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1996,14 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="n">
-        <v>500</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>500/96</t>
+        </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>500 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>500/96 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -1982,12 +2030,14 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>75</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>75/0</t>
+        </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>75 TEXTURISED POLYESTER</t>
+          <t>75/0 TEXTURISED POLYESTER</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2064,14 @@
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>75</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>75/36</t>
+        </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>75 LMY POLYESTER</t>
+          <t>75/36 LMY POLYESTER</t>
         </is>
       </c>
     </row>
@@ -2046,12 +2098,14 @@
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>840</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>840/140</t>
+        </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 6 YARN</t>
+          <t>840/140 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -2078,12 +2132,14 @@
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>840</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>840/140</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>840 HI-TENACITY NYLON 6 YARN</t>
+          <t>840/140 HI-TENACITY NYLON 6 YARN</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2166,14 @@
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="n">
-        <v>840</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>840/144</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>840 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>840/144 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2200,14 @@
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="n">
-        <v>840</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>840/144</t>
+        </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>840 SHT CONTINOUS POLYESTER FILAMENT</t>
+          <t>840/144 SHT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2234,14 @@
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="n">
-        <v>840</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>840/192</t>
+        </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>840 HT CONTINOUS POLYESTER FILAMENT</t>
+          <t>840/192 HT CONTINOUS POLYESTER FILAMENT</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2268,44 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="n">
-        <v>210</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>210/24</t>
+        </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>210 HI-TENACITY NYLON 6 YARN</t>
+          <t>210/24 HI-TENACITY NYLON 6 YARN</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1000000230</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>75/2-POLYESTER-YARN</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TEXTURISED POLYESTER</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>75/2</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>75/2 TEXTURISED POLYESTER</t>
         </is>
       </c>
     </row>
